--- a/backend/data/financials_by_company/0FK.F.xlsx
+++ b/backend/data/financials_by_company/0FK.F.xlsx
@@ -3260,10 +3260,8 @@
           <t>Jakarta</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12430</t>
-        </is>
+      <c r="D2" t="n">
+        <v>12430</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3458,7 +3456,7 @@
         <v>-1565000</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
         <v>2.134</v>
@@ -3671,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO2" t="n">
         <v>-0.00122</v>
